--- a/data/ams_weekly_data/Audio_Array/ads_report_week20.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week20.xlsx
@@ -16167,10 +16167,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13544.33333333333</v>
+        <v>13544</v>
       </c>
       <c r="E7" t="n">
-        <v>76.66666666666667</v>
+        <v>77</v>
       </c>
       <c r="F7" t="n">
         <v>1538.733333333333</v>
@@ -16179,7 +16179,7 @@
         <v>4960.453333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>3.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -16200,10 +16200,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13544.33333333333</v>
+        <v>13544</v>
       </c>
       <c r="E8" t="n">
-        <v>76.66666666666667</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
         <v>1538.733333333333</v>
@@ -16212,7 +16212,7 @@
         <v>4960.453333333334</v>
       </c>
       <c r="H8" t="n">
-        <v>3.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -16233,10 +16233,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13544.33333333333</v>
+        <v>13544</v>
       </c>
       <c r="E9" t="n">
-        <v>76.66666666666667</v>
+        <v>77</v>
       </c>
       <c r="F9" t="n">
         <v>1538.733333333333</v>
@@ -16245,7 +16245,7 @@
         <v>4960.453333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>3.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -16365,10 +16365,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16980.33333333333</v>
+        <v>16980</v>
       </c>
       <c r="E13" t="n">
-        <v>99.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
         <v>2229.913333333333</v>
@@ -16377,7 +16377,7 @@
         <v>5048.873333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -16398,10 +16398,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16980.33333333333</v>
+        <v>16980</v>
       </c>
       <c r="E14" t="n">
-        <v>99.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
         <v>2229.913333333333</v>
@@ -16410,7 +16410,7 @@
         <v>5048.873333333334</v>
       </c>
       <c r="H14" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -16431,10 +16431,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16980.33333333333</v>
+        <v>16980</v>
       </c>
       <c r="E15" t="n">
-        <v>99.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
         <v>2229.913333333333</v>
@@ -16443,7 +16443,7 @@
         <v>5048.873333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2.333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -16464,19 +16464,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E16" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G16" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -16497,19 +16497,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E17" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G17" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -16530,19 +16530,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E18" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G18" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -16563,19 +16563,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E19" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G19" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -16596,19 +16596,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E20" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F20" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G20" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -16629,19 +16629,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E21" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G21" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -16662,19 +16662,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E22" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G22" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -16695,19 +16695,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E23" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G23" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -16728,19 +16728,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E24" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G24" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -16761,19 +16761,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E25" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G25" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -16794,19 +16794,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E26" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F26" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G26" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -16827,19 +16827,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E27" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G27" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -16860,19 +16860,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E28" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F28" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G28" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -16893,19 +16893,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E29" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G29" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -16926,19 +16926,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E30" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G30" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -16959,19 +16959,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E31" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F31" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G31" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -16992,19 +16992,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E32" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G32" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -17025,19 +17025,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E33" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G33" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -17058,19 +17058,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E34" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F34" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G34" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -17091,19 +17091,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E35" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G35" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -17124,19 +17124,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E36" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F36" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G36" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -17157,19 +17157,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E37" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F37" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G37" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -17190,19 +17190,19 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E38" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F38" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G38" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -17223,19 +17223,19 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E39" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G39" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -17256,19 +17256,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E40" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F40" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G40" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -17289,19 +17289,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E41" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F41" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G41" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -17322,19 +17322,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E42" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F42" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G42" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -17355,19 +17355,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E43" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G43" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -17388,19 +17388,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1448.793103448276</v>
+        <v>1435</v>
       </c>
       <c r="E44" t="n">
-        <v>10.75862068965517</v>
+        <v>11</v>
       </c>
       <c r="F44" t="n">
         <v>274.5910344827586</v>
       </c>
       <c r="G44" t="n">
-        <v>347.6331034482759</v>
+        <v>347.6331034482758</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1724137931034483</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week20.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week20.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
